--- a/exports/503_union-cuviriaki.xlsx
+++ b/exports/503_union-cuviriaki.xlsx
@@ -1935,22 +1935,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>23682483</t>
+          <t>63150971</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARANCIBIA</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OSPINA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>YANZU ALIN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1959,16 +1959,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15/08/1960</t>
+          <t>27/03/2012</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02/09/2013</t>
+          <t>09/04/2013</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>63150971</t>
+          <t>81263369</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>YANZU ALIN</t>
+          <t>ROBERTO ADAN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>27/03/2012</t>
+          <t>11/10/2014</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>09/04/2013</t>
+          <t>01/04/2015</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>81263369</t>
+          <t>90780494</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,25 +2076,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ROBERTO ADAN</t>
+          <t>ZIOREMA MARIANA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11/10/2014</t>
+          <t>18/05/2018</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>18/05/2023</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>90780494</t>
+          <t>61751029</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2134,30 +2134,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ZIOREMA MARIANA</t>
+          <t>KELVIN MOISES</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18/05/2018</t>
+          <t>12/04/2011</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18/05/2023</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>61751029</t>
+          <t>80952132</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KELVIN MOISES</t>
+          <t>YAMILA ANAHI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12/04/2011</t>
+          <t>27/08/2013</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>31/05/2014</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>80952132</t>
+          <t>90606046</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YAMILA ANAHI</t>
+          <t>YARIT ARIELI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>27/08/2013</t>
+          <t>30/01/2018</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31/05/2014</t>
+          <t>30/01/2023</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>90606046</t>
+          <t>94703180</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>YARIT ARIELI</t>
+          <t>RAIZEL ALAIA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>30/01/2018</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>30/01/2023</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,7 +2376,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>94703180</t>
+          <t>45779794</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2386,35 +2386,35 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RAIZEL ALAIA</t>
+          <t>ROLANDO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>13/04/1985</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>45779794</t>
+          <t>46488655</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2454,20 +2454,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ROLANDO</t>
+          <t>CELIA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13/04/1985</t>
+          <t>08/04/1988</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>46488655</t>
+          <t>47952177</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2517,20 +2517,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t>ADAN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>08/04/1988</t>
+          <t>26/01/1991</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>05/03/2013</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>47952177</t>
+          <t>74364562</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2575,30 +2575,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VILA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ADAN</t>
+          <t>JHEMINA CESIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>26/01/1991</t>
+          <t>20/10/2002</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>05/03/2013</t>
+          <t>14/01/2012</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>74364562</t>
+          <t>74364561</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JHEMINA CESIA</t>
+          <t>CALEB JOSUE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20/10/2002</t>
+          <t>03/01/2005</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>14/01/2012</t>
+          <t>11/01/2012</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>74364561</t>
+          <t>63248750</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CALEB JOSUE</t>
+          <t>ABIGAIL JHONSU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>03/01/2005</t>
+          <t>06/05/2012</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>11/01/2012</t>
+          <t>30/05/2014</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>63248750</t>
+          <t>90686642</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ABIGAIL JHONSU</t>
+          <t>ALESSIA AMELI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2778,16 +2778,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>06/05/2012</t>
+          <t>20/03/2018</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>30/05/2014</t>
+          <t>20/03/2023</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,45 +2817,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>90686642</t>
+          <t>71676297</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>ARMES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VILA</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ALESSIA AMELI</t>
+          <t>JEAN PIERO ALEXANDER</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20/03/2018</t>
+          <t>29/09/2005</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>20/03/2023</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>71676297</t>
+          <t>20581372</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2890,30 +2890,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JEAN PIERO ALEXANDER</t>
+          <t>ALEJANDRINA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>29/09/2005</t>
+          <t>03/05/1954</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,35 +2943,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20581372</t>
+          <t>19878654</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ARMES</t>
+          <t>ARONES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YAÑEZ</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ALEJANDRINA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>03/05/1954</t>
+          <t>10/12/1934</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>06/03/2014</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,45 +3006,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19878654</t>
+          <t>71715085</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARONES</t>
+          <t>ASCENCIO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>QUIRIGUA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>EUDES CLEDY</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10/12/1934</t>
+          <t>01/05/1997</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>06/03/2014</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,35 +3069,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>71715085</t>
+          <t>77051476</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASCENCIO</t>
+          <t>ASTULLA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>QUIRIGUA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EUDES CLEDY</t>
+          <t>JESUS MARLON</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01/05/1997</t>
+          <t>14/04/2006</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,40 +3132,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>77051476</t>
+          <t>45178734</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ASTULLA</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JESUS MARLON</t>
+          <t>YANET YENI</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14/04/2006</t>
+          <t>26/06/1984</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>20/01/2023</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>45178734</t>
+          <t>77381246</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>YANET YENI</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3219,21 +3219,21 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>26/06/1984</t>
+          <t>15/04/1997</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>20/01/2023</t>
+          <t>09/02/2012</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,40 +3258,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>77381246</t>
+          <t>20416330</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>ATAU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>RAFAEL DEMESIO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>15/04/1997</t>
+          <t>18/07/1964</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20416330</t>
+          <t>44931709</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ATAU</t>
+          <t>ATAVILLOS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RAFAEL DEMESIO</t>
+          <t>BEKER</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,16 +3345,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/07/1964</t>
+          <t>18/08/1986</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>09/02/2012</t>
+          <t>07/10/2020</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,45 +3384,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>44931709</t>
+          <t>60102789</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ATAVILLOS</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>LLANES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BEKER</t>
+          <t>EMELY YEILY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/1986</t>
+          <t>08/07/2007</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>07/10/2020</t>
+          <t>18/06/2013</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,7 +3447,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>60102789</t>
+          <t>21004100</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3457,35 +3457,35 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LLANES</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EMELY YEILY</t>
+          <t>MAURO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>08/07/2007</t>
+          <t>02/08/1974</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18/06/2013</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21004100</t>
+          <t>21003956</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3525,20 +3525,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MAURO</t>
+          <t>GLADYS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>02/08/1974</t>
+          <t>20/06/1976</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21003956</t>
+          <t>45733059</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GLADYS</t>
+          <t>DORIS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20/06/1976</t>
+          <t>25/02/1989</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>04/11/2013</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>45733059</t>
+          <t>47831380</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DORIS</t>
+          <t>NILDA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>25/02/1989</t>
+          <t>23/04/1992</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>04/11/2013</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>47831380</t>
+          <t>62218016</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>PIONGA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NILDA</t>
+          <t>LIZ DEYSI</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>23/04/1992</t>
+          <t>28/01/1997</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>62218016</t>
+          <t>62218014</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,20 +3777,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LIZ DEYSI</t>
+          <t>WILIAN HURTADO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>28/01/1997</t>
+          <t>07/06/1998</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>62218014</t>
+          <t>62218015</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>WILIAN HURTADO</t>
+          <t>NORVI OSWALDO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3849,11 +3849,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>07/06/1998</t>
+          <t>24/10/1999</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>62218015</t>
+          <t>62218020</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NORVI OSWALDO</t>
+          <t>OCLIDES YORDIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>24/10/1999</t>
+          <t>08/07/2003</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>62218020</t>
+          <t>62218021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OCLIDES YORDIN</t>
+          <t>LADWIN RUCNEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,11 +3975,11 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>08/07/2003</t>
+          <t>08/07/2006</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>62218021</t>
+          <t>62218019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LADWIN RUCNEL</t>
+          <t>KEDINSON DEINEL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,11 +4038,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>08/07/2006</t>
+          <t>11/04/2008</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>62218019</t>
+          <t>61667591</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4092,25 +4092,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KEDINSON DEINEL</t>
+          <t>BERTLI YEVIS</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11/04/2008</t>
+          <t>19/07/2010</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4140,7 +4140,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>61667591</t>
+          <t>80838274</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BERTLI YEVIS</t>
+          <t>CARLA MELINDA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4164,11 +4164,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19/07/2010</t>
+          <t>07/06/2013</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>03/05/2016</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>80838274</t>
+          <t>80838279</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CARLA MELINDA</t>
+          <t>NICOL ANICA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4227,16 +4227,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>07/06/2013</t>
+          <t>29/05/2015</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>80838279</t>
+          <t>91122085</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NICOL ANICA</t>
+          <t>ELVIA MALDI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29/05/2015</t>
+          <t>05/01/2019</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>03/05/2016</t>
+          <t>05/01/2024</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>91122085</t>
+          <t>94066826</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ELVIA MALDI</t>
+          <t>MALUCKKYTHA ROLANNDA CHESSY</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,11 +4353,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>05/01/2019</t>
+          <t>09/12/2024</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>05/01/2024</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>94066826</t>
+          <t>20978430</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4402,35 +4402,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PIONGA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MALUCKKYTHA ROLANNDA CHESSY</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>05/02/1953</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,35 +4455,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20978430</t>
+          <t>20979746</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DE FABIAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>MARINA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>05/02/1953</t>
+          <t>30/08/1950</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>15/01/2014</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20979746</t>
+          <t>21008225</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>AYSANA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DE FABIAN</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MARINA</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,21 +4542,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>30/08/1950</t>
+          <t>17/06/1969</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>15/01/2014</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,45 +4581,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21008225</t>
+          <t>20003068</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AYSANA</t>
+          <t>BALBUENA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ROSA</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>17/06/1969</t>
+          <t>27/12/1949</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>04/03/2014</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,35 +4644,35 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20003068</t>
+          <t>20999840</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BALBUENA</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>DE MENDEZ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>ISABEL ANTONIA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>27/12/1949</t>
+          <t>06/07/1965</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>04/03/2014</t>
+          <t>01/07/2013</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,45 +4707,45 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20999840</t>
+          <t>43141667</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DE MENDEZ</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ISABEL ANTONIA</t>
+          <t>DIONISIO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>06/07/1965</t>
+          <t>10/02/1980</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>01/07/2013</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,7 +4770,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>43141667</t>
+          <t>61159761</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4780,35 +4780,35 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>MONTERO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>PAMELA VIANET</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>10/02/1980</t>
+          <t>12/11/2007</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>61159761</t>
+          <t>81206475</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4848,30 +4848,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PAMELA VIANET</t>
+          <t>ANGHELO KENNY</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>12/11/2007</t>
+          <t>28/09/2013</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>03/07/2014</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>81206475</t>
+          <t>76363361</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MONTERO</t>
+          <t>TUMAYLLA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ANGHELO KENNY</t>
+          <t>HEBER</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>28/09/2013</t>
+          <t>04/01/1995</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>03/07/2014</t>
+          <t>06/06/2012</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,27 +4959,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>76363361</t>
+          <t>74144942</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BELLIDO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TUMAYLLA</t>
+          <t>BISAREZ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HEBER</t>
+          <t>CANDY SOLEDAD</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>04/01/1995</t>
+          <t>02/09/1995</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>06/06/2012</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,7 +5022,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>74144942</t>
+          <t>90998766</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5032,35 +5032,35 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BISAREZ</t>
+          <t>ZELARAYAN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CANDY SOLEDAD</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>02/09/1995</t>
+          <t>10/10/2018</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>10/10/2023</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,40 +5085,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>90998766</t>
+          <t>46841244</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BELLIDO</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ZELARAYAN</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>BETSABEL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>10/10/2018</t>
+          <t>14/03/1991</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>10/10/2023</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,35 +5148,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>46841244</t>
+          <t>44133425</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>CABEZAS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BETSABEL</t>
+          <t>ODON</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14/03/1991</t>
+          <t>26/01/1986</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>08/10/2020</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>92514471</t>
+          <t>63264907</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>CAHUANA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ARECHE</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EYDAN ORIEL</t>
+          <t>JEFREY MABRIX</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>30/08/2021</t>
+          <t>18/08/2001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>07/10/2020</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,22 +5274,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>44133425</t>
+          <t>74856610</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CABEZAS</t>
+          <t>CAHUANA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ODON</t>
+          <t>JHEYZON HOMAR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>26/01/1986</t>
+          <t>17/09/2005</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>08/10/2020</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,27 +5337,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>63264907</t>
+          <t>75589359</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CAHUANA</t>
+          <t>CAISAHUANA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JEFREY MABRIX</t>
+          <t>WENDY GEOVANA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/08/2001</t>
+          <t>09/09/2001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>07/10/2020</t>
+          <t>24/04/2024</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>74856610</t>
+          <t>60002571</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAHUANA</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JHEYZON HOMAR</t>
+          <t>VICENTE ABDY</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,11 +5424,11 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/09/2005</t>
+          <t>26/12/2006</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5463,45 +5463,45 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>75589359</t>
+          <t>61692759</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CAISAHUANA</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>WENDY GEOVANA</t>
+          <t>ALIN DANY</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>09/09/2001</t>
+          <t>29/08/2009</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>24/04/2024</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>60002571</t>
+          <t>76854353</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VICENTE ABDY</t>
+          <t>DAYSI SHIRLEY</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>26/12/2006</t>
+          <t>18/02/2003</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>61692759</t>
+          <t>62042759</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CANCHARI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ALIN DANY</t>
+          <t>JORDAN MAYKOL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>29/08/2009</t>
+          <t>01/06/2009</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,45 +5652,45 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>76854353</t>
+          <t>20741903</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>MAIS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DAYSI SHIRLEY</t>
+          <t>ERLI ELIVER</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/02/2003</t>
+          <t>01/11/1975</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>06/06/2012</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>62042759</t>
+          <t>61159680</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CANCHARI</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JORDAN MAYKOL</t>
+          <t>MAIKER TITO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,16 +5739,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>01/06/2009</t>
+          <t>03/09/2007</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,22 +5778,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20741903</t>
+          <t>07637339</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MAIS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ERLI ELIVER</t>
+          <t>LUIS AUGUSTO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,11 +5802,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>01/11/1975</t>
+          <t>03/08/1974</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>06/06/2012</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07637339</t>
+          <t>19826452</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CARHUAS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LUIS AUGUSTO</t>
+          <t>VALENTIN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>03/08/1974</t>
+          <t>16/07/1947</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>11/03/2014</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,35 +5904,35 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>19826452</t>
+          <t>19820806</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CARHUAS</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>VISCARRA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VALENTIN</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>16/07/1947</t>
+          <t>12/05/1964</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>11/03/2014</t>
+          <t>16/06/2016</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,35 +5967,35 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>19820806</t>
+          <t>19817125</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VISCARRA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>MARCELINO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12/05/1964</t>
+          <t>04/02/1960</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>16/06/2016</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,45 +6030,45 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>19817125</t>
+          <t>80838252</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MARCELINO</t>
+          <t>LISCETH ANALI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>04/02/1960</t>
+          <t>16/10/2011</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>04/11/2013</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>80838252</t>
+          <t>20710330</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>OSORIO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LISCETH ANALI</t>
+          <t>MAURA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,21 +6117,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>16/10/2011</t>
+          <t>11/05/1967</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>04/11/2013</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20710330</t>
+          <t>20584185</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CCONOVILCA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OSORIO</t>
+          <t>LAIME</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>MAURA</t>
+          <t>FELIPA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,11 +6180,11 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>11/05/1967</t>
+          <t>23/08/1971</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20584185</t>
+          <t>21014039</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CCONOVILCA</t>
+          <t>CELESTINO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LAIME</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>FELIPA</t>
+          <t>LUZ ELIZABETH</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23/08/1971</t>
+          <t>21/04/1978</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>06/06/2012</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>21014039</t>
+          <t>44464660</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LUZ ELIZABETH</t>
+          <t>ROXANA JUANA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>21/04/1978</t>
+          <t>08/05/1987</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>06/06/2012</t>
+          <t>22/04/2013</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>44464660</t>
+          <t>47240371</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6360,20 +6360,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ROXANA JUANA</t>
+          <t>RICHARSON HECTOR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>08/05/1987</t>
+          <t>05/08/1992</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>22/04/2013</t>
+          <t>21/12/2012</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,7 +6408,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>47240371</t>
+          <t>73360192</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>RICHARSON HECTOR</t>
+          <t>JOSE ROGER</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6432,16 +6432,16 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>05/08/1992</t>
+          <t>28/07/2004</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>21/12/2012</t>
+          <t>16/08/2013</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>73360192</t>
+          <t>20581459</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>JOSE ROGER</t>
+          <t>VIRGILIO JUSTINO</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,16 +6495,16 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>28/07/2004</t>
+          <t>26/09/1958</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>16/08/2013</t>
+          <t>13/06/2014</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,45 +6534,45 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>20581459</t>
+          <t>94012790</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CELESTINO</t>
+          <t>CHACUPE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VIRGILIO JUSTINO</t>
+          <t>LUCIANA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>26/09/1958</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>13/06/2014</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,12 +6597,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>94012790</t>
+          <t>63150948</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CHACUPE</t>
+          <t>CHAHUA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LUCIANA</t>
+          <t>MARIELA YANDY</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>15/02/2012</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,7 +6660,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>63150948</t>
+          <t>79519083</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6675,30 +6675,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>MARIELA YANDY</t>
+          <t>KENYI JHONIER</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>15/02/2012</t>
+          <t>31/01/2016</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>31/05/2016</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,7 +6723,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>79519083</t>
+          <t>46081983</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>QUILCA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KENYI JHONIER</t>
+          <t>ROMULO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,16 +6747,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>31/01/2016</t>
+          <t>23/11/1989</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>31/05/2016</t>
+          <t>26/02/2018</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,7 +6786,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>46081983</t>
+          <t>20591933</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>QUILCA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ROMULO</t>
+          <t>VENANCIO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>23/11/1989</t>
+          <t>27/02/1967</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>26/02/2018</t>
+          <t>05/08/2014</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,7 +6849,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20591933</t>
+          <t>74349047</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6859,35 +6859,35 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SALVATIERRA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VENANCIO</t>
+          <t>DANIELA HERMELINDA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>27/02/1967</t>
+          <t>24/10/2004</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>05/08/2014</t>
+          <t>28/06/2020</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>74349047</t>
+          <t>60483669</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6927,20 +6927,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DANIELA HERMELINDA</t>
+          <t>YORDAN</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>24/10/2004</t>
+          <t>08/03/2007</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>28/06/2020</t>
+          <t>16/01/2012</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,35 +6975,35 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>60483669</t>
+          <t>78718922</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CHAHUA</t>
+          <t>CHIRA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>PUMACAHUA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>YORDAN</t>
+          <t>DORIS RUDY</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>08/03/2007</t>
+          <t>20/12/1998</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>16/01/2012</t>
+          <t>28/01/2015</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,22 +7038,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>78718922</t>
+          <t>74554336</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CHIRA</t>
+          <t>CHOCCE</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PUMACAHUA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DORIS RUDY</t>
+          <t>ESTEFANI ALEXANDRA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20/12/1998</t>
+          <t>13/05/2001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>28/01/2015</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>74554336</t>
+          <t>91426782</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CHOCCE</t>
+          <t>CHORIHUANTY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ICAROA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ESTEFANI ALEXANDRA</t>
+          <t>KATHERINE RUTH</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,16 +7125,16 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>13/05/2001</t>
+          <t>24/07/2019</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>14/08/2024</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,45 +7164,45 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>91426782</t>
+          <t>61256066</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CHORIHUANTY</t>
+          <t>CHUPAYO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ICAROA</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>KATHERINE RUTH</t>
+          <t>DEYSON BRAYAN</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>24/07/2019</t>
+          <t>11/04/2008</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>14/08/2024</t>
+          <t>21/02/2013</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,7 +7227,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>61256066</t>
+          <t>62731745</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7242,30 +7242,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DEYSON BRAYAN</t>
+          <t>NAYELY YANIRA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>11/04/2008</t>
+          <t>05/05/2011</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>62731745</t>
+          <t>81392956</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NAYELY YANIRA</t>
+          <t>SURIELA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>05/05/2011</t>
+          <t>03/07/2013</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>21/02/2013</t>
+          <t>06/06/2014</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>81392956</t>
+          <t>42435611</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7363,30 +7363,30 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SURIELA</t>
+          <t>MELCIADES JERSON</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>03/07/2013</t>
+          <t>13/04/1980</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>06/06/2014</t>
+          <t>21/02/2013</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>42435611</t>
+          <t>41805944</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CHUPAYO</t>
+          <t>COMANTI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>MELCIADES JERSON</t>
+          <t>GOÑE OSWALDO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,11 +7440,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>13/04/1980</t>
+          <t>04/07/1983</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>21/02/2013</t>
+          <t>24/10/2018</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>41805944</t>
+          <t>20978974</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GOÑE OSWALDO</t>
+          <t>ESTEBAN</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>04/07/1983</t>
+          <t>15/03/1961</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>24/10/2018</t>
+          <t>22/10/2013</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>20978974</t>
+          <t>45356960</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>COMANTI</t>
+          <t>CONDE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t>LANASCA DE QUINTO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ESTEBAN</t>
+          <t>REYNALDA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>15/03/1961</t>
+          <t>12/10/1985</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>22/10/2013</t>
+          <t>11/01/2012</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>45356960</t>
+          <t>60804122</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CONDE</t>
+          <t>CONDOR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LANASCA DE QUINTO</t>
+          <t>PAREDEZ</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>REYNALDA</t>
+          <t>JUAN GUSTAVO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>12/10/1985</t>
+          <t>11/11/2006</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>11/01/2012</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>60804122</t>
+          <t>23653765</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7678,35 +7678,35 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PAREDEZ</t>
+          <t>YANGALI</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>JUAN GUSTAVO</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>11/11/2006</t>
+          <t>11/05/1963</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>01/07/2013</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,22 +7731,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>23653765</t>
+          <t>61652177</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CONDOR</t>
+          <t>CONDORI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>YANGALI</t>
+          <t>MANDUJANO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>LALESKA SARAI</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>11/05/1963</t>
+          <t>08/06/2009</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>01/07/2013</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>61652177</t>
+          <t>90964154</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7809,30 +7809,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LALESKA SARAI</t>
+          <t>HOXVAR MABEL</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>08/06/2009</t>
+          <t>18/09/2018</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,7 +7857,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>90964154</t>
+          <t>44835977</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MANDUJANO</t>
+          <t>NOLIVOS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>HOXVAR MABEL</t>
+          <t>ABEL PITER</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7881,16 +7881,16 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>18/09/2018</t>
+          <t>08/09/1982</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>22/06/2015</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,22 +7920,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>44835977</t>
+          <t>75826588</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CONDORI</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NOLIVOS</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ABEL PITER</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,21 +7944,21 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>08/09/1982</t>
+          <t>01/03/2006</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>22/06/2015</t>
+          <t>14/01/2012</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>75826588</t>
+          <t>62232520</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7998,20 +7998,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>DEYSI ANGELICA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>01/03/2006</t>
+          <t>10/02/2008</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>62232520</t>
+          <t>63260156</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DEYSI ANGELICA</t>
+          <t>SOLEDAD BETTY</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>10/02/2008</t>
+          <t>11/02/2011</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>14/01/2012</t>
+          <t>04/11/2013</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>63260156</t>
+          <t>78191012</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SOLEDAD BETTY</t>
+          <t>ROSALIA ANDREA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>11/02/2011</t>
+          <t>13/07/2013</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>04/11/2013</t>
+          <t>05/05/2015</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>78191012</t>
+          <t>79532770</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ROSALIA ANDREA</t>
+          <t>DARY GABRIEL</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>13/07/2013</t>
+          <t>13/02/2016</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>05/05/2015</t>
+          <t>28/04/2016</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>79532770</t>
+          <t>45618482</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DARY GABRIEL</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,16 +8259,16 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>13/02/2016</t>
+          <t>15/03/1985</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>28/04/2016</t>
+          <t>14/03/2013</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,7 +8298,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>45618482</t>
+          <t>45682529</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>ELVIS</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>15/03/1985</t>
+          <t>10/04/1987</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>14/03/2013</t>
+          <t>14/01/2012</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,7 +8361,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>45682529</t>
+          <t>76856404</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ELVIS</t>
+          <t>SIMEON LUIS</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10/04/1987</t>
+          <t>28/02/1995</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>14/01/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,7 +8424,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>76856404</t>
+          <t>78010743</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SIMEON LUIS</t>
+          <t>FIDEL ANGEL</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,11 +8448,11 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>28/02/1995</t>
+          <t>29/09/1996</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8487,7 +8487,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>78010743</t>
+          <t>61407203</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8502,25 +8502,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>FIDEL ANGEL</t>
+          <t>SANDRA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>29/09/1996</t>
+          <t>08/11/1998</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>09/02/2012</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>61407203</t>
+          <t>78655618</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SANDRA</t>
+          <t>MILIZET BRIGITT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>08/11/1998</t>
+          <t>22/01/2014</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>09/02/2012</t>
+          <t>03/11/2015</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>78655618</t>
+          <t>60105695</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8623,35 +8623,35 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MILIZET BRIGITT</t>
+          <t>KENY</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22/01/2014</t>
+          <t>22/01/2005</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>03/11/2015</t>
+          <t>28/06/2020</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,7 +8676,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>60105695</t>
+          <t>92545158</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>KENY</t>
+          <t>HEUSS ADRIAN</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>22/01/2005</t>
+          <t>19/09/2021</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>28/06/2020</t>
+          <t>20/10/2021</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>92545158</t>
+          <t>19986519</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>RODRIGO</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>HEUSS ADRIAN</t>
+          <t>FLORENCIO</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8763,21 +8763,21 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>19/09/2021</t>
+          <t>02/02/1959</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>20/10/2021</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>19986519</t>
+          <t>94137577</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>RODRIGO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>FLORENCIO</t>
+          <t>HANS JUNIOR</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8826,21 +8826,21 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>02/02/1959</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>17/02/2025</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,22 +8865,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>94137577</t>
+          <t>80444996</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>COSHANTE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MOTIGRE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>HANS JUNIOR</t>
+          <t>ROGER</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>04/03/1979</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>17/02/2025</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,35 +8928,35 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>80444996</t>
+          <t>60701769</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>COSHANTE</t>
+          <t>CRISPIN</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MOTIGRE</t>
+          <t>BARBARAN</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ROGER</t>
+          <t>ELVIA</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>04/03/1979</t>
+          <t>03/03/1996</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,7 +8991,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>60701769</t>
+          <t>46910956</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9001,25 +9001,25 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BARBARAN</t>
+          <t>BUJAICO</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ELVIA</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>03/03/1996</t>
+          <t>27/12/1990</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>17/06/2019</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,7 +9054,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>46910956</t>
+          <t>79237427</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9064,35 +9064,35 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BUJAICO</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>SAYUMI MEHA</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>27/12/1990</t>
+          <t>15/07/2015</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>17/06/2019</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>79237427</t>
+          <t>41422993</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CRISPIN</t>
+          <t>CULLANCO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SAYUMI MEHA</t>
+          <t>NANCY MERCEDES</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,16 +9141,16 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>15/07/2015</t>
+          <t>23/06/1982</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12834,22 +12834,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>90730331</t>
+          <t>61376216</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>YANTAS</t>
+          <t>LAVIO</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DREICK LIAM</t>
+          <t>LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12858,16 +12858,16 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>21/03/2018</t>
+          <t>25/05/2008</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12897,45 +12897,45 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>61376216</t>
+          <t>20995288</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>LAVIO</t>
+          <t>RETIS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE</t>
+          <t>CLEBERLINDA SANTA</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>25/05/2008</t>
+          <t>08/03/1973</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>27/01/2020</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12960,7 +12960,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>20995288</t>
+          <t>20996967</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>CLEBERLINDA SANTA</t>
+          <t>ENMA MONICA</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12984,11 +12984,11 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>08/03/1973</t>
+          <t>12/08/1974</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>27/01/2020</t>
+          <t>10/04/2017</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13023,7 +13023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>20996967</t>
+          <t>20961730</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13033,30 +13033,30 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>RETIS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ENMA MONICA</t>
+          <t>ARTURO ACEVEDO</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>12/08/1974</t>
+          <t>09/09/1948</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>10/04/2017</t>
+          <t>07/04/2014</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13086,22 +13086,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>20961730</t>
+          <t>20080163</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>GUILLEN</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ARTURO ACEVEDO</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>09/09/1948</t>
+          <t>14/05/1966</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>07/04/2014</t>
+          <t>23/11/2011</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13149,40 +13149,40 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>20080163</t>
+          <t>41453371</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GUILLEN</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>SANDRA VILMA</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>14/05/1966</t>
+          <t>06/01/1982</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>23/11/2011</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13212,22 +13212,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>41453371</t>
+          <t>21010839</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>SANDRA VILMA</t>
+          <t>LIZ SUSANA</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13236,11 +13236,11 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>06/01/1982</t>
+          <t>12/02/1977</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>03/02/2012</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13275,22 +13275,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>21010839</t>
+          <t>20993254</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>HUACHACA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>DE MEDINA</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LIZ SUSANA</t>
+          <t>DIONISIA</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13299,11 +13299,11 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>12/02/1977</t>
+          <t>10/06/1968</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>03/02/2012</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13338,7 +13338,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>20993254</t>
+          <t>41917062</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13348,12 +13348,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DE MEDINA</t>
+          <t>MATAMOROS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>DIONISIA</t>
+          <t>CARLA CECILIA</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13362,11 +13362,11 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>10/06/1968</t>
+          <t>14/07/1981</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>08/04/2014</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13401,45 +13401,45 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>41917062</t>
+          <t>61115067</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HUACHACA</t>
+          <t>HUAJA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>MATAMOROS</t>
+          <t>CONGORA</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>CARLA CECILIA</t>
+          <t>ALVARO LEONARDO</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>14/07/1981</t>
+          <t>24/07/2007</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>08/04/2014</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13464,22 +13464,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>61115067</t>
+          <t>43651566</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HUAJA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CONGORA</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ALVARO LEONARDO</t>
+          <t>ASAEL EFRAIN</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13488,16 +13488,16 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>24/07/2007</t>
+          <t>06/05/1982</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13527,7 +13527,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>43651566</t>
+          <t>43627759</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>DIONISIO</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ASAEL EFRAIN</t>
+          <t>DENNYS JACK</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>06/05/1982</t>
+          <t>30/01/1982</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>25/02/2013</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13590,7 +13590,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>43627759</t>
+          <t>23453896</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13600,25 +13600,25 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>DENNYS JACK</t>
+          <t>FORTUNATA</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>30/01/1982</t>
+          <t>03/06/1970</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>25/02/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13653,7 +13653,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>23453896</t>
+          <t>60423210</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>FORTUNATA</t>
+          <t>DAYANA LOREN</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13677,21 +13677,21 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>03/06/1970</t>
+          <t>02/07/2006</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13716,7 +13716,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>60423210</t>
+          <t>63233881</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13731,30 +13731,30 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DAYANA LOREN</t>
+          <t>DAYRON ANDY</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>02/07/2006</t>
+          <t>16/03/2012</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13779,7 +13779,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>63233881</t>
+          <t>75528599</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13789,35 +13789,35 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>DAYRON ANDY</t>
+          <t>YULISA ANDREA</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>16/03/2012</t>
+          <t>20/03/1999</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>16/08/2013</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13842,7 +13842,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>75528599</t>
+          <t>44576842</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>YULISA ANDREA</t>
+          <t>DELIA LUISA</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13866,21 +13866,21 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>20/03/1999</t>
+          <t>22/06/1981</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>16/08/2013</t>
+          <t>25/04/2020</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13905,7 +13905,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>44576842</t>
+          <t>76600042</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SILVESTRE</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>DELIA LUISA</t>
+          <t>RITMAR</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13929,16 +13929,16 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>22/06/1981</t>
+          <t>08/01/1998</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>25/04/2020</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13968,45 +13968,45 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>76600042</t>
+          <t>44604306</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUANCAUQUI</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SILVESTRE</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>RITMAR</t>
+          <t>JAVIER MANUEL</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>08/01/1998</t>
+          <t>24/12/1985</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14031,45 +14031,45 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>44604306</t>
+          <t>80838251</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HUANCAUQUI</t>
+          <t>HUAPI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>JAVIER MANUEL</t>
+          <t>NILA EVELIN</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>24/12/1985</t>
+          <t>14/06/2011</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14094,45 +14094,45 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>80838251</t>
+          <t>43864471</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HUAPI</t>
+          <t>HUAYNACCERO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>CORONADO</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NILA EVELIN</t>
+          <t>ALAN ROLANDO</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>14/06/2011</t>
+          <t>03/04/1986</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>RESIDENTES CC.PP. FOCALIZADOS (DL N° 1164)</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>08/04/2016</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14157,7 +14157,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>43864471</t>
+          <t>79487345</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CORONADO</t>
+          <t>PIONGA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ALAN ROLANDO</t>
+          <t>YIMI</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -14181,21 +14181,21 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>03/04/1986</t>
+          <t>02/02/2015</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>RESIDENTES CC.PP. FOCALIZADOS (DL N° 1164)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>08/04/2016</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -14220,22 +14220,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>79487345</t>
+          <t>79349774</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HUAYNACCERO</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>PIONGA</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>YIMI</t>
+          <t>EZEL NEMIAS</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>02/02/2015</t>
+          <t>21/10/2015</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>21/05/2021</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14283,7 +14283,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>79349774</t>
+          <t>90546559</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>EZEL NEMIAS</t>
+          <t>VICTORINO ISRAEL</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -14307,11 +14307,11 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>21/10/2015</t>
+          <t>20/12/2017</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>21/05/2021</t>
+          <t>04/01/2023</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14346,7 +14346,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>90546559</t>
+          <t>44023950</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>BLANCAS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VICTORINO ISRAEL</t>
+          <t>NEMIAS SANTOS</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -14370,16 +14370,16 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>20/12/2017</t>
+          <t>07/06/1981</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>04/01/2023</t>
+          <t>19/12/2017</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14409,7 +14409,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>44023950</t>
+          <t>43260515</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14424,20 +14424,20 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NEMIAS SANTOS</t>
+          <t>ELENA ELISA</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>07/06/1981</t>
+          <t>14/11/1985</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>19/12/2017</t>
+          <t>21/02/2013</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14472,7 +14472,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>43260515</t>
+          <t>46210942</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ELENA ELISA</t>
+          <t>LIDIA</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14496,11 +14496,11 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>14/11/1985</t>
+          <t>22/10/1987</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14535,7 +14535,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>46210942</t>
+          <t>60804024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LIDIA</t>
+          <t>MAYLI SHEYLA</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>22/10/1987</t>
+          <t>28/07/2006</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14598,35 +14598,35 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>60804024</t>
+          <t>61256005</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>BLANCAS</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>MAYLI SHEYLA</t>
+          <t>BRECK BAYER</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>28/07/2006</t>
+          <t>15/02/2008</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>21/02/2013</t>
+          <t>04/09/2013</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14661,7 +14661,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>61256005</t>
+          <t>79122299</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14671,35 +14671,35 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>BRECK BAYER</t>
+          <t>ALENDA ROCIO</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>15/02/2008</t>
+          <t>14/05/2015</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>04/09/2013</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14724,22 +14724,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>79122299</t>
+          <t>40521787</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>INGUNZA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ALENDA ROCIO</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -14748,21 +14748,21 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>14/05/2015</t>
+          <t>18/11/1977</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14787,45 +14787,45 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>40521787</t>
+          <t>63399386</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>INGUNZA</t>
+          <t>IZURRAGA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>AARON JHOSHIMAR</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>18/11/1977</t>
+          <t>07/12/2011</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -28076,7 +28076,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>76153245</t>
+          <t>73392100</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -28086,17 +28086,17 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>LAUREANO</t>
+          <t>TUPALAYA</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>ELIANA KARINA</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F440" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>30/09/1995</t>
+          <t>06/11/1995</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -28139,7 +28139,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>73392100</t>
+          <t>61055800</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -28149,12 +28149,12 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>TUPALAYA</t>
+          <t>VIVAS</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>LUIS ERIK</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -28163,21 +28163,21 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>06/11/1995</t>
+          <t>13/12/2007</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -28187,7 +28187,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>09/06/2022</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -28202,7 +28202,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>61055800</t>
+          <t>74425178</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28212,25 +28212,25 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>VIVAS</t>
+          <t>ÑAHUINCOPA</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>LUIS ERIK</t>
+          <t>MELISIA YOBANA</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F442" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>13/12/2007</t>
+          <t>13/09/2003</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28250,7 +28250,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>09/06/2022</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">

--- a/exports/503_union-cuviriaki.xlsx
+++ b/exports/503_union-cuviriaki.xlsx
@@ -1935,22 +1935,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>63150971</t>
+          <t>23682483</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>ARANCIBIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>OSPINA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>YANZU ALIN</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1959,16 +1959,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>27/03/2012</t>
+          <t>15/08/1960</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>09/04/2013</t>
+          <t>02/09/2013</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>81263369</t>
+          <t>63150971</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ROBERTO ADAN</t>
+          <t>YANZU ALIN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11/10/2014</t>
+          <t>27/03/2012</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>01/04/2015</t>
+          <t>09/04/2013</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>90780494</t>
+          <t>81263369</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,25 +2076,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ZIOREMA MARIANA</t>
+          <t>ROBERTO ADAN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18/05/2018</t>
+          <t>11/10/2014</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18/05/2023</t>
+          <t>01/04/2015</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>61751029</t>
+          <t>90780494</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2134,30 +2134,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KELVIN MOISES</t>
+          <t>ZIOREMA MARIANA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12/04/2011</t>
+          <t>18/05/2018</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>18/05/2023</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>80952132</t>
+          <t>61751029</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>YAMILA ANAHI</t>
+          <t>KELVIN MOISES</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>27/08/2013</t>
+          <t>12/04/2011</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31/05/2014</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>90606046</t>
+          <t>80952132</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YARIT ARIELI</t>
+          <t>YAMILA ANAHI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>30/01/2018</t>
+          <t>27/08/2013</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>30/01/2023</t>
+          <t>31/05/2014</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>94703180</t>
+          <t>90606046</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RAIZEL ALAIA</t>
+          <t>YARIT ARIELI</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>30/01/2018</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>30/01/2023</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,7 +2376,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45779794</t>
+          <t>94703180</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2386,35 +2386,35 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ROLANDO</t>
+          <t>RAIZEL ALAIA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>13/04/1985</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>03/07/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>46488655</t>
+          <t>45779794</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2454,20 +2454,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t>ROLANDO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>08/04/1988</t>
+          <t>13/04/1985</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,7 +2502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>47952177</t>
+          <t>46488655</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2517,20 +2517,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ADAN</t>
+          <t>CELIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>26/01/1991</t>
+          <t>08/04/1988</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>05/03/2013</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>74364562</t>
+          <t>47952177</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2575,30 +2575,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VILA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JHEMINA CESIA</t>
+          <t>ADAN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20/10/2002</t>
+          <t>26/01/1991</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>14/01/2012</t>
+          <t>05/03/2013</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>74364561</t>
+          <t>74364562</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,20 +2643,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CALEB JOSUE</t>
+          <t>JHEMINA CESIA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>03/01/2005</t>
+          <t>20/10/2002</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>11/01/2012</t>
+          <t>14/01/2012</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>63248750</t>
+          <t>74364561</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ABIGAIL JHONSU</t>
+          <t>CALEB JOSUE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>06/05/2012</t>
+          <t>03/01/2005</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30/05/2014</t>
+          <t>11/01/2012</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>90686642</t>
+          <t>63248750</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ALESSIA AMELI</t>
+          <t>ABIGAIL JHONSU</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2778,16 +2778,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20/03/2018</t>
+          <t>06/05/2012</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>20/03/2023</t>
+          <t>30/05/2014</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,45 +2817,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>71676297</t>
+          <t>90686642</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ARMES</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CABRERA</t>
+          <t>VILA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JEAN PIERO ALEXANDER</t>
+          <t>ALESSIA AMELI</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29/09/2005</t>
+          <t>20/03/2018</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>20/03/2023</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20581372</t>
+          <t>71676297</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2890,30 +2890,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YAÑEZ</t>
+          <t>CABRERA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ALEJANDRINA</t>
+          <t>JEAN PIERO ALEXANDER</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>03/05/1954</t>
+          <t>29/09/2005</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,35 +2943,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>19878654</t>
+          <t>20581372</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ARONES</t>
+          <t>ARMES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>ALEJANDRINA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/12/1934</t>
+          <t>03/05/1954</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>06/03/2014</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,45 +3006,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>71715085</t>
+          <t>19878654</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ASCENCIO</t>
+          <t>ARONES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>QUIRIGUA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EUDES CLEDY</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01/05/1997</t>
+          <t>10/12/1934</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>06/03/2014</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,35 +3069,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>77051476</t>
+          <t>71715085</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASTULLA</t>
+          <t>ASCENCIO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>QUIRIGUA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JESUS MARLON</t>
+          <t>EUDES CLEDY</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14/04/2006</t>
+          <t>01/05/1997</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,40 +3132,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>45178734</t>
+          <t>77051476</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ATAO</t>
+          <t>ASTULLA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>YANET YENI</t>
+          <t>JESUS MARLON</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>26/06/1984</t>
+          <t>14/04/2006</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20/01/2023</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>77381246</t>
+          <t>45178734</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>YANET YENI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3219,21 +3219,21 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>15/04/1997</t>
+          <t>26/06/1984</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>09/02/2012</t>
+          <t>20/01/2023</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,40 +3258,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20416330</t>
+          <t>77381246</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ATAU</t>
+          <t>ATAO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RAFAEL DEMESIO</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/07/1964</t>
+          <t>15/04/1997</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>44931709</t>
+          <t>20416330</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ATAVILLOS</t>
+          <t>ATAU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BEKER</t>
+          <t>RAFAEL DEMESIO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,16 +3345,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/08/1986</t>
+          <t>18/07/1964</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>07/10/2020</t>
+          <t>09/02/2012</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,45 +3384,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>60102789</t>
+          <t>44931709</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>ATAVILLOS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LLANES</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EMELY YEILY</t>
+          <t>BEKER</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>08/07/2007</t>
+          <t>18/08/1986</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18/06/2013</t>
+          <t>07/10/2020</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,7 +3447,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21004100</t>
+          <t>60102789</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3457,35 +3457,35 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>LLANES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MAURO</t>
+          <t>EMELY YEILY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>02/08/1974</t>
+          <t>08/07/2007</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>18/06/2013</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21003956</t>
+          <t>21004100</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3525,20 +3525,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GLADYS</t>
+          <t>MAURO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20/06/1976</t>
+          <t>02/08/1974</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>45733059</t>
+          <t>21003956</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DORIS</t>
+          <t>GLADYS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25/02/1989</t>
+          <t>20/06/1976</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>04/11/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>47831380</t>
+          <t>45733059</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NILDA</t>
+          <t>DORIS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>23/04/1992</t>
+          <t>25/02/1989</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>04/11/2013</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>62218016</t>
+          <t>47831380</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PIONGA</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LIZ DEYSI</t>
+          <t>NILDA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>28/01/1997</t>
+          <t>23/04/1992</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>62218014</t>
+          <t>62218016</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,20 +3777,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>WILIAN HURTADO</t>
+          <t>LIZ DEYSI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>07/06/1998</t>
+          <t>28/01/1997</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>62218015</t>
+          <t>62218014</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NORVI OSWALDO</t>
+          <t>WILIAN HURTADO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3849,11 +3849,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>24/10/1999</t>
+          <t>07/06/1998</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>62218020</t>
+          <t>62218015</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OCLIDES YORDIN</t>
+          <t>NORVI OSWALDO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>08/07/2003</t>
+          <t>24/10/1999</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>62218021</t>
+          <t>62218020</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LADWIN RUCNEL</t>
+          <t>OCLIDES YORDIN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,11 +3975,11 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>08/07/2006</t>
+          <t>08/07/2003</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>62218019</t>
+          <t>62218021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KEDINSON DEINEL</t>
+          <t>LADWIN RUCNEL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,11 +4038,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11/04/2008</t>
+          <t>08/07/2006</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>61667591</t>
+          <t>62218019</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4092,25 +4092,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BERTLI YEVIS</t>
+          <t>KEDINSON DEINEL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19/07/2010</t>
+          <t>11/04/2008</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4140,7 +4140,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>80838274</t>
+          <t>61667591</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CARLA MELINDA</t>
+          <t>BERTLI YEVIS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4164,11 +4164,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>07/06/2013</t>
+          <t>19/07/2010</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>03/05/2016</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>80838279</t>
+          <t>80838274</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NICOL ANICA</t>
+          <t>CARLA MELINDA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4227,16 +4227,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>29/05/2015</t>
+          <t>07/06/2013</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>91122085</t>
+          <t>80838279</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ELVIA MALDI</t>
+          <t>NICOL ANICA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>05/01/2019</t>
+          <t>29/05/2015</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>05/01/2024</t>
+          <t>03/05/2016</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>94066826</t>
+          <t>91122085</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MALUCKKYTHA ROLANNDA CHESSY</t>
+          <t>ELVIA MALDI</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,11 +4353,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>05/01/2019</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>05/01/2024</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20978430</t>
+          <t>94066826</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4402,35 +4402,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PIONGA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>MALUCKKYTHA ROLANNDA CHESSY</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>05/02/1953</t>
+          <t>09/12/2024</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,35 +4455,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20979746</t>
+          <t>20978430</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DE FABIAN</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MARINA</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>30/08/1950</t>
+          <t>05/02/1953</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>15/01/2014</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,22 +4518,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21008225</t>
+          <t>20979746</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AYSANA</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>DE FABIAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ROSA</t>
+          <t>MARINA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,21 +4542,21 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>17/06/1969</t>
+          <t>30/08/1950</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>15/01/2014</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,45 +4581,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20003068</t>
+          <t>21008225</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BALBUENA</t>
+          <t>AYSANA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>ROSA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>27/12/1949</t>
+          <t>17/06/1969</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>04/03/2014</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,35 +4644,35 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20999840</t>
+          <t>20003068</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>BALBUENA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DE MENDEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ISABEL ANTONIA</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>06/07/1965</t>
+          <t>27/12/1949</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>01/07/2013</t>
+          <t>04/03/2014</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,45 +4707,45 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>43141667</t>
+          <t>20999840</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>DE MENDEZ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>ISABEL ANTONIA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10/02/1980</t>
+          <t>06/07/1965</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>01/07/2013</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,7 +4770,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>61159761</t>
+          <t>43141667</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4780,35 +4780,35 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MONTERO</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PAMELA VIANET</t>
+          <t>DIONISIO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>12/11/2007</t>
+          <t>10/02/1980</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>81206475</t>
+          <t>61159761</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4848,30 +4848,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ANGHELO KENNY</t>
+          <t>PAMELA VIANET</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>28/09/2013</t>
+          <t>12/11/2007</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>03/07/2014</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>76363361</t>
+          <t>81206475</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TUMAYLLA</t>
+          <t>MONTERO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>HEBER</t>
+          <t>ANGHELO KENNY</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>04/01/1995</t>
+          <t>28/09/2013</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>06/06/2012</t>
+          <t>03/07/2014</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,27 +4959,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>74144942</t>
+          <t>76363361</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BELLIDO</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BISAREZ</t>
+          <t>TUMAYLLA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CANDY SOLEDAD</t>
+          <t>HEBER</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>02/09/1995</t>
+          <t>04/01/1995</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>06/06/2012</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,7 +5022,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>90998766</t>
+          <t>74144942</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5032,35 +5032,35 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ZELARAYAN</t>
+          <t>BISAREZ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>CANDY SOLEDAD</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>10/10/2018</t>
+          <t>02/09/1995</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>10/10/2023</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,40 +5085,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>46841244</t>
+          <t>90998766</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>BELLIDO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>ZELARAYAN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BETSABEL</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14/03/1991</t>
+          <t>10/10/2018</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>10/10/2023</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,35 +5148,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>44133425</t>
+          <t>46841244</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CABEZAS</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ODON</t>
+          <t>BETSABEL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>26/01/1986</t>
+          <t>14/03/1991</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>08/10/2020</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>63264907</t>
+          <t>92514471</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CAHUANA</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>ARECHE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JEFREY MABRIX</t>
+          <t>EYDAN ORIEL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2001</t>
+          <t>30/08/2021</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>07/10/2020</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,22 +5274,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>74856610</t>
+          <t>44133425</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CAHUANA</t>
+          <t>CABEZAS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JHEYZON HOMAR</t>
+          <t>ODON</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/09/2005</t>
+          <t>26/01/1986</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>08/10/2020</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,27 +5337,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>75589359</t>
+          <t>63264907</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CAISAHUANA</t>
+          <t>CAHUANA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>WENDY GEOVANA</t>
+          <t>JEFREY MABRIX</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>09/09/2001</t>
+          <t>18/08/2001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>24/04/2024</t>
+          <t>07/10/2020</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>60002571</t>
+          <t>74856610</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CAHUANA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VICENTE ABDY</t>
+          <t>JHEYZON HOMAR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,11 +5424,11 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>26/12/2006</t>
+          <t>17/09/2005</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5463,45 +5463,45 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>61692759</t>
+          <t>75589359</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CAISAHUANA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ALIN DANY</t>
+          <t>WENDY GEOVANA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>29/08/2009</t>
+          <t>09/09/2001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>24/04/2024</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>76854353</t>
+          <t>60002571</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DAYSI SHIRLEY</t>
+          <t>VICENTE ABDY</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/02/2003</t>
+          <t>26/12/2006</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>62042759</t>
+          <t>61692759</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CANCHARI</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JORDAN MAYKOL</t>
+          <t>ALIN DANY</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>01/06/2009</t>
+          <t>29/08/2009</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,45 +5652,45 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20741903</t>
+          <t>76854353</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MAIS</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ERLI ELIVER</t>
+          <t>DAYSI SHIRLEY</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>01/11/1975</t>
+          <t>18/02/2003</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>06/06/2012</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>61159680</t>
+          <t>62042759</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CANCHARI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MAIKER TITO</t>
+          <t>JORDAN MAYKOL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,16 +5739,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>03/09/2007</t>
+          <t>01/06/2009</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,22 +5778,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07637339</t>
+          <t>20741903</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MAIS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LUIS AUGUSTO</t>
+          <t>ERLI ELIVER</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,11 +5802,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>03/08/1974</t>
+          <t>01/11/1975</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>06/06/2012</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>19826452</t>
+          <t>07637339</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CARHUAS</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VALENTIN</t>
+          <t>LUIS AUGUSTO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,21 +5865,21 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>16/07/1947</t>
+          <t>03/08/1974</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>11/03/2014</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,35 +5904,35 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>19820806</t>
+          <t>19826452</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>CARHUAS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VISCARRA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>GLORIA</t>
+          <t>VALENTIN</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>12/05/1964</t>
+          <t>16/07/1947</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>16/06/2016</t>
+          <t>11/03/2014</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,35 +5967,35 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>19817125</t>
+          <t>19820806</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>VISCARRA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MARCELINO</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>04/02/1960</t>
+          <t>12/05/1964</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>16/06/2016</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,45 +6030,45 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>80838252</t>
+          <t>19817125</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LISCETH ANALI</t>
+          <t>MARCELINO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>16/10/2011</t>
+          <t>04/02/1960</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>04/11/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>20710330</t>
+          <t>80838252</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OSORIO</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MAURA</t>
+          <t>LISCETH ANALI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,21 +6117,21 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>11/05/1967</t>
+          <t>16/10/2011</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>04/11/2013</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>20584185</t>
+          <t>20710330</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CCONOVILCA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LAIME</t>
+          <t>OSORIO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>FELIPA</t>
+          <t>MAURA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,11 +6180,11 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23/08/1971</t>
+          <t>11/05/1967</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACIÓN MASIVA JUNTOS DE SISFOH</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>21014039</t>
+          <t>20584185</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CELESTINO</t>
+          <t>CCONOVILCA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>LAIME</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LUZ ELIZABETH</t>
+          <t>FELIPA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>21/04/1978</t>
+          <t>23/08/1971</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>06/06/2012</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>44464660</t>
+          <t>21014039</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ROXANA JUANA</t>
+          <t>LUZ ELIZABETH</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>08/05/1987</t>
+          <t>21/04/1978</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>22/04/2013</t>
+          <t>06/06/2012</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>47240371</t>
+          <t>44464660</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6360,20 +6360,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>RICHARSON HECTOR</t>
+          <t>ROXANA JUANA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>05/08/1992</t>
+          <t>08/05/1987</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>21/12/2012</t>
+          <t>22/04/2013</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,7 +6408,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>73360192</t>
+          <t>47240371</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>JOSE ROGER</t>
+          <t>RICHARSON HECTOR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6432,16 +6432,16 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>28/07/2004</t>
+          <t>05/08/1992</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>16/08/2013</t>
+          <t>21/12/2012</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20581459</t>
+          <t>73360192</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VIRGILIO JUSTINO</t>
+          <t>JOSE ROGER</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,16 +6495,16 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>26/09/1958</t>
+          <t>28/07/2004</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>13/06/2014</t>
+          <t>16/08/2013</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,45 +6534,45 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>94012790</t>
+          <t>20581459</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CHACUPE</t>
+          <t>CELESTINO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LUCIANA</t>
+          <t>VIRGILIO JUSTINO</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>26/09/1958</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>13/06/2014</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,12 +6597,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>63150948</t>
+          <t>94012790</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CHAHUA</t>
+          <t>CHACUPE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>MARIELA YANDY</t>
+          <t>LUCIANA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>15/02/2012</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>15/10/2012</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,7 +6660,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>79519083</t>
+          <t>63150948</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6675,30 +6675,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KENYI JHONIER</t>
+          <t>MARIELA YANDY</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>31/01/2016</t>
+          <t>15/02/2012</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>31/05/2016</t>
+          <t>15/10/2012</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,7 +6723,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>46081983</t>
+          <t>79519083</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>QUILCA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ROMULO</t>
+          <t>KENYI JHONIER</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,16 +6747,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>23/11/1989</t>
+          <t>31/01/2016</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>26/02/2018</t>
+          <t>31/05/2016</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,7 +6786,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20591933</t>
+          <t>46081983</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>QUILCA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VENANCIO</t>
+          <t>ROMULO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>27/02/1967</t>
+          <t>23/11/1989</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>05/08/2014</t>
+          <t>26/02/2018</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,7 +6849,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>74349047</t>
+          <t>20591933</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6859,35 +6859,35 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DANIELA HERMELINDA</t>
+          <t>VENANCIO</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>24/10/2004</t>
+          <t>27/02/1967</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>28/06/2020</t>
+          <t>05/08/2014</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>60483669</t>
+          <t>74349047</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6927,20 +6927,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>YORDAN</t>
+          <t>DANIELA HERMELINDA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>08/03/2007</t>
+          <t>24/10/2004</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>16/01/2012</t>
+          <t>28/06/2020</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,35 +6975,35 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>78718922</t>
+          <t>60483669</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CHIRA</t>
+          <t>CHAHUA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PUMACAHUA</t>
+          <t>SALVATIERRA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DORIS RUDY</t>
+          <t>YORDAN</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20/12/1998</t>
+          <t>08/03/2007</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>28/01/2015</t>
+          <t>16/01/2012</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,22 +7038,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>74554336</t>
+          <t>78718922</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CHOCCE</t>
+          <t>CHIRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PUMACAHUA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ESTEFANI ALEXANDRA</t>
+          <t>DORIS RUDY</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>13/05/2001</t>
+          <t>20/12/1998</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>28/01/2015</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>91426782</t>
+          <t>74554336</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CHORIHUANTY</t>
+          <t>CHOCCE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ICAROA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>KATHERINE RUTH</t>
+          <t>ESTEFANI ALEXANDRA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,16 +7125,16 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>24/07/2019</t>
+          <t>13/05/2001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>14/08/2024</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,45 +7164,45 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>61256066</t>
+          <t>91426782</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CHUPAYO</t>
+          <t>CHORIHUANTY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>ICAROA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DEYSON BRAYAN</t>
+          <t>KATHERINE RUTH</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>11/04/2008</t>
+          <t>24/07/2019</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>21/02/2013</t>
+          <t>14/08/2024</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,7 +7227,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>62731745</t>
+          <t>61256066</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7242,30 +7242,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NAYELY YANIRA</t>
+          <t>DEYSON BRAYAN</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>05/05/2011</t>
+          <t>11/04/2008</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>81392956</t>
+          <t>62731745</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SURIELA</t>
+          <t>NAYELY YANIRA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>03/07/2013</t>
+          <t>05/05/2011</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>06/06/2014</t>
+          <t>21/02/2013</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>42435611</t>
+          <t>81392956</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7363,30 +7363,30 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VICENTE</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>MELCIADES JERSON</t>
+          <t>SURIELA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>13/04/1980</t>
+          <t>03/07/2013</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>21/02/2013</t>
+          <t>06/06/2014</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>41805944</t>
+          <t>42435611</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>COMANTI</t>
+          <t>CHUPAYO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VICENTE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GOÑE OSWALDO</t>
+          <t>MELCIADES JERSON</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,11 +7440,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>04/07/1983</t>
+          <t>13/04/1980</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>24/10/2018</t>
+          <t>21/02/2013</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>20978974</t>
+          <t>41805944</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ESTEBAN</t>
+          <t>GOÑE OSWALDO</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>15/03/1961</t>
+          <t>04/07/1983</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>22/10/2013</t>
+          <t>24/10/2018</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>45356960</t>
+          <t>20978974</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CONDE</t>
+          <t>COMANTI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LANASCA DE QUINTO</t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>REYNALDA</t>
+          <t>ESTEBAN</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>12/10/1985</t>
+          <t>15/03/1961</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>11/01/2012</t>
+          <t>22/10/2013</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>60804122</t>
+          <t>45356960</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CONDOR</t>
+          <t>CONDE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PAREDEZ</t>
+          <t>LANASCA DE QUINTO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>JUAN GUSTAVO</t>
+          <t>REYNALDA</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>11/11/2006</t>
+          <t>12/10/1985</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>11/01/2012</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,7 +7668,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>23653765</t>
+          <t>60804122</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7678,35 +7678,35 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>YANGALI</t>
+          <t>PAREDEZ</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>JUAN GUSTAVO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>11/05/1963</t>
+          <t>11/11/2006</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>01/07/2013</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,22 +7731,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>61652177</t>
+          <t>23653765</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CONDORI</t>
+          <t>CONDOR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MANDUJANO</t>
+          <t>YANGALI</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LALESKA SARAI</t>
+          <t>JUANA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>08/06/2009</t>
+          <t>11/05/1963</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>01/07/2013</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>90964154</t>
+          <t>61652177</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7809,30 +7809,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>HOXVAR MABEL</t>
+          <t>LALESKA SARAI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>18/09/2018</t>
+          <t>08/06/2009</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,7 +7857,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>44835977</t>
+          <t>90964154</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NOLIVOS</t>
+          <t>MANDUJANO</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ABEL PITER</t>
+          <t>HOXVAR MABEL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7881,16 +7881,16 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>08/09/1982</t>
+          <t>18/09/2018</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>22/06/2015</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,22 +7920,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>75826588</t>
+          <t>44835977</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>CONDORI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>NOLIVOS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>ABEL PITER</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,21 +7944,21 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>01/03/2006</t>
+          <t>08/09/1982</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>14/01/2012</t>
+          <t>22/06/2015</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>62232520</t>
+          <t>75826588</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7998,20 +7998,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DEYSI ANGELICA</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>10/02/2008</t>
+          <t>01/03/2006</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>63260156</t>
+          <t>62232520</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SOLEDAD BETTY</t>
+          <t>DEYSI ANGELICA</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>11/02/2011</t>
+          <t>10/02/2008</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>04/11/2013</t>
+          <t>14/01/2012</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>78191012</t>
+          <t>63260156</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ROSALIA ANDREA</t>
+          <t>SOLEDAD BETTY</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>13/07/2013</t>
+          <t>11/02/2011</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>05/05/2015</t>
+          <t>04/11/2013</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>79532770</t>
+          <t>78191012</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>DARY GABRIEL</t>
+          <t>ROSALIA ANDREA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>13/02/2016</t>
+          <t>13/07/2013</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>28/04/2016</t>
+          <t>05/05/2015</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>45618482</t>
+          <t>79532770</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CRISTHIAN</t>
+          <t>DARY GABRIEL</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,16 +8259,16 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>15/03/1985</t>
+          <t>13/02/2016</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>14/03/2013</t>
+          <t>28/04/2016</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,7 +8298,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>45682529</t>
+          <t>45618482</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ELVIS</t>
+          <t>CRISTHIAN</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10/04/1987</t>
+          <t>15/03/1985</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>14/01/2012</t>
+          <t>14/03/2013</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,7 +8361,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>76856404</t>
+          <t>45682529</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SIMEON LUIS</t>
+          <t>ELVIS</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>28/02/1995</t>
+          <t>10/04/1987</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/01/2012</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,7 +8424,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>78010743</t>
+          <t>76856404</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>FIDEL ANGEL</t>
+          <t>SIMEON LUIS</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,11 +8448,11 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>29/09/1996</t>
+          <t>28/02/1995</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8487,7 +8487,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>61407203</t>
+          <t>78010743</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8502,25 +8502,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SANDRA</t>
+          <t>FIDEL ANGEL</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>08/11/1998</t>
+          <t>29/09/1996</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>09/02/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>78655618</t>
+          <t>61407203</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MILIZET BRIGITT</t>
+          <t>SANDRA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>22/01/2014</t>
+          <t>08/11/1998</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>03/11/2015</t>
+          <t>09/02/2012</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>60105695</t>
+          <t>78655618</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8623,35 +8623,35 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>KENY</t>
+          <t>MILIZET BRIGITT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>22/01/2005</t>
+          <t>22/01/2014</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>28/06/2020</t>
+          <t>03/11/2015</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,7 +8676,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>92545158</t>
+          <t>60105695</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>HEUSS ADRIAN</t>
+          <t>KENY</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>19/09/2021</t>
+          <t>22/01/2005</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>20/10/2021</t>
+          <t>28/06/2020</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,7 +8739,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>19986519</t>
+          <t>92545158</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>RODRIGO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>FLORENCIO</t>
+          <t>HEUSS ADRIAN</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8763,21 +8763,21 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>02/02/1959</t>
+          <t>19/09/2021</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>20/10/2021</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>94137577</t>
+          <t>19986519</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGO</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>HANS JUNIOR</t>
+          <t>FLORENCIO</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8826,21 +8826,21 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>02/02/1959</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>17/02/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,22 +8865,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>80444996</t>
+          <t>94137577</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>COSHANTE</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MOTIGRE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ROGER</t>
+          <t>HANS JUNIOR</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>04/03/1979</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>17/02/2025</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,35 +8928,35 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>60701769</t>
+          <t>80444996</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CRISPIN</t>
+          <t>COSHANTE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BARBARAN</t>
+          <t>MOTIGRE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ELVIA</t>
+          <t>ROGER</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>03/03/1996</t>
+          <t>04/03/1979</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,7 +8991,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>46910956</t>
+          <t>60701769</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9001,25 +9001,25 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BUJAICO</t>
+          <t>BARBARAN</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>ELVIA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>27/12/1990</t>
+          <t>03/03/1996</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>17/06/2019</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,7 +9054,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>79237427</t>
+          <t>46910956</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9064,35 +9064,35 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>BUJAICO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SAYUMI MEHA</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>15/07/2015</t>
+          <t>27/12/1990</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>12/09/2020</t>
+          <t>17/06/2019</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>41422993</t>
+          <t>79237427</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CULLANCO</t>
+          <t>CRISPIN</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NANCY MERCEDES</t>
+          <t>SAYUMI MEHA</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,16 +9141,16 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>23/06/1982</t>
+          <t>15/07/2015</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>12/09/2020</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12834,22 +12834,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>61376216</t>
+          <t>90730331</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>LAVIO</t>
+          <t>YANTAS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE</t>
+          <t>DREICK LIAM</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12858,16 +12858,16 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>25/05/2008</t>
+          <t>21/03/2018</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12897,45 +12897,45 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>20995288</t>
+          <t>61376216</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>GONZALES</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>RETIS</t>
+          <t>LAVIO</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>CLEBERLINDA SANTA</t>
+          <t>LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>08/03/1973</t>
+          <t>25/05/2008</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>27/01/2020</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12960,7 +12960,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>20996967</t>
+          <t>20995288</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ENMA MONICA</t>
+          <t>CLEBERLINDA SANTA</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12984,11 +12984,11 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>12/08/1974</t>
+          <t>08/03/1973</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>10/04/2017</t>
+          <t>27/01/2020</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -13023,7 +13023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>20961730</t>
+          <t>20996967</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13033,30 +13033,30 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RETIS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>ARTURO ACEVEDO</t>
+          <t>ENMA MONICA</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>09/09/1948</t>
+          <t>12/08/1974</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>07/04/2014</t>
+          <t>10/04/2017</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -13086,22 +13086,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>20080163</t>
+          <t>20961730</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GUILLEN</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>ARTURO ACEVEDO</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>14/05/1966</t>
+          <t>09/09/1948</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>23/11/2011</t>
+          <t>07/04/2014</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13149,40 +13149,40 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>41453371</t>
+          <t>20080163</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GUILLEN</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>SANDRA VILMA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>06/01/1982</t>
+          <t>14/05/1966</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>23/11/2011</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -13212,22 +13212,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>21010839</t>
+          <t>41453371</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>MALPARTIDA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LIZ SUSANA</t>
+          <t>SANDRA VILMA</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13236,11 +13236,11 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>12/02/1977</t>
+          <t>06/01/1982</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>03/02/2012</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13275,22 +13275,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>20993254</t>
+          <t>21010839</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HUACHACA</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DE MEDINA</t>
+          <t>MALPARTIDA</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>DIONISIA</t>
+          <t>LIZ SUSANA</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13299,11 +13299,11 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>10/06/1968</t>
+          <t>12/02/1977</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>03/02/2012</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13338,7 +13338,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>41917062</t>
+          <t>20993254</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13348,12 +13348,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MATAMOROS</t>
+          <t>DE MEDINA</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>CARLA CECILIA</t>
+          <t>DIONISIA</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13362,11 +13362,11 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>14/07/1981</t>
+          <t>10/06/1968</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>08/04/2014</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13401,45 +13401,45 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>61115067</t>
+          <t>41917062</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HUAJA</t>
+          <t>HUACHACA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CONGORA</t>
+          <t>MATAMOROS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ALVARO LEONARDO</t>
+          <t>CARLA CECILIA</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>24/07/2007</t>
+          <t>14/07/1981</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>11/02/2025</t>
+          <t>08/04/2014</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13464,22 +13464,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>43651566</t>
+          <t>61115067</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HUAJA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BENDEZU</t>
+          <t>CONGORA</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ASAEL EFRAIN</t>
+          <t>ALVARO LEONARDO</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13488,16 +13488,16 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>06/05/1982</t>
+          <t>24/07/2007</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>11/02/2025</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13527,7 +13527,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>43627759</t>
+          <t>43651566</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>BENDEZU</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>DENNYS JACK</t>
+          <t>ASAEL EFRAIN</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>30/01/1982</t>
+          <t>06/05/1982</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>25/02/2013</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13590,7 +13590,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>23453896</t>
+          <t>43627759</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13600,25 +13600,25 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>DIONISIO</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>FORTUNATA</t>
+          <t>DENNYS JACK</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>03/06/1970</t>
+          <t>30/01/1982</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>25/02/2013</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13653,7 +13653,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>60423210</t>
+          <t>23453896</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DAYANA LOREN</t>
+          <t>FORTUNATA</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13677,21 +13677,21 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>02/07/2006</t>
+          <t>03/06/1970</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>12/06/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13716,7 +13716,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>63233881</t>
+          <t>60423210</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13731,30 +13731,30 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>DAYRON ANDY</t>
+          <t>DAYANA LOREN</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>16/03/2012</t>
+          <t>02/07/2006</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>12/06/2012</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13779,7 +13779,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>75528599</t>
+          <t>63233881</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13789,35 +13789,35 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>YULISA ANDREA</t>
+          <t>DAYRON ANDY</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>20/03/1999</t>
+          <t>16/03/2012</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>16/08/2013</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13842,7 +13842,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>44576842</t>
+          <t>75528599</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>DELIA LUISA</t>
+          <t>YULISA ANDREA</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13866,21 +13866,21 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>22/06/1981</t>
+          <t>20/03/1999</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>25/04/2020</t>
+          <t>16/08/2013</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13905,7 +13905,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>76600042</t>
+          <t>44576842</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SILVESTRE</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>RITMAR</t>
+          <t>DELIA LUISA</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13929,16 +13929,16 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>08/01/1998</t>
+          <t>22/06/1981</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>25/04/2020</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13968,45 +13968,45 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>44604306</t>
+          <t>76600042</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HUANCAUQUI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>SILVESTRE</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>JAVIER MANUEL</t>
+          <t>RITMAR</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>24/12/1985</t>
+          <t>08/01/1998</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -14031,45 +14031,45 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>80838251</t>
+          <t>44604306</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HUAPI</t>
+          <t>HUANCAUQUI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ATILIO</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NILA EVELIN</t>
+          <t>JAVIER MANUEL</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>14/06/2011</t>
+          <t>24/12/1985</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>24/04/2013</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14094,45 +14094,45 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>43864471</t>
+          <t>80838251</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HUAYNACCERO</t>
+          <t>HUAPI</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>CORONADO</t>
+          <t>ATILIO</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ALAN ROLANDO</t>
+          <t>NILA EVELIN</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>03/04/1986</t>
+          <t>14/06/2011</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>RESIDENTES CC.PP. FOCALIZADOS (DL N° 1164)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14142,7 +14142,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>08/04/2016</t>
+          <t>24/04/2013</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14157,7 +14157,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>79487345</t>
+          <t>43864471</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>PIONGA</t>
+          <t>CORONADO</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>YIMI</t>
+          <t>ALAN ROLANDO</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -14181,21 +14181,21 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>02/02/2015</t>
+          <t>03/04/1986</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>RESIDENTES CC.PP. FOCALIZADOS (DL N° 1164)</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>08/04/2016</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -14220,22 +14220,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>79349774</t>
+          <t>79487345</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>HUAYNACCERO</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>BERROCAL</t>
+          <t>PIONGA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>EZEL NEMIAS</t>
+          <t>YIMI</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>21/10/2015</t>
+          <t>02/02/2015</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>21/05/2021</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14283,7 +14283,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>90546559</t>
+          <t>79349774</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VICTORINO ISRAEL</t>
+          <t>EZEL NEMIAS</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -14307,11 +14307,11 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>20/12/2017</t>
+          <t>21/10/2015</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>04/01/2023</t>
+          <t>21/05/2021</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14346,7 +14346,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>44023950</t>
+          <t>90546559</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>BLANCAS</t>
+          <t>BERROCAL</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NEMIAS SANTOS</t>
+          <t>VICTORINO ISRAEL</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -14370,16 +14370,16 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>07/06/1981</t>
+          <t>20/12/2017</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>19/12/2017</t>
+          <t>04/01/2023</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14409,7 +14409,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>43260515</t>
+          <t>44023950</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14424,20 +14424,20 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ELENA ELISA</t>
+          <t>NEMIAS SANTOS</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>14/11/1985</t>
+          <t>07/06/1981</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>21/02/2013</t>
+          <t>19/12/2017</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14472,7 +14472,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>46210942</t>
+          <t>43260515</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LIDIA</t>
+          <t>ELENA ELISA</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14496,11 +14496,11 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>22/10/1987</t>
+          <t>14/11/1985</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14535,7 +14535,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>60804024</t>
+          <t>46210942</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>MAYLI SHEYLA</t>
+          <t>LIDIA</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14559,21 +14559,21 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>28/07/2006</t>
+          <t>22/10/1987</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14598,35 +14598,35 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>61256005</t>
+          <t>60804024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>BLANCAS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>BRECK BAYER</t>
+          <t>MAYLI SHEYLA</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>15/02/2008</t>
+          <t>28/07/2006</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>04/09/2013</t>
+          <t>21/02/2013</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14661,7 +14661,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>79122299</t>
+          <t>61256005</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14671,35 +14671,35 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ALENDA ROCIO</t>
+          <t>BRECK BAYER</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>14/05/2015</t>
+          <t>15/02/2008</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/09/2013</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14724,22 +14724,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>40521787</t>
+          <t>79122299</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>INGUNZA</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>ALENDA ROCIO</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -14748,21 +14748,21 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>18/11/1977</t>
+          <t>14/05/2015</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14772,7 +14772,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>04/03/2013</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14787,45 +14787,45 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>63399386</t>
+          <t>40521787</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IZURRAGA</t>
+          <t>INGUNZA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AARON JHOSHIMAR</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>07/12/2011</t>
+          <t>18/11/1977</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>04/03/2013</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -28076,7 +28076,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>73392100</t>
+          <t>76153245</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -28086,17 +28086,17 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>TUPALAYA</t>
+          <t>LAUREANO</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>ELIANA KARINA</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F440" t="n">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>06/11/1995</t>
+          <t>30/09/1995</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -28139,7 +28139,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>61055800</t>
+          <t>73392100</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -28149,12 +28149,12 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>VIVAS</t>
+          <t>TUPALAYA</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>LUIS ERIK</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -28163,21 +28163,21 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>13/12/2007</t>
+          <t>06/11/1995</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -28187,7 +28187,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>09/06/2022</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -28202,7 +28202,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>74425178</t>
+          <t>61055800</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28212,25 +28212,25 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>ÑAHUINCOPA</t>
+          <t>VIVAS</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>MELISIA YOBANA</t>
+          <t>LUIS ERIK</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F442" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>13/09/2003</t>
+          <t>13/12/2007</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28250,7 +28250,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>09/06/2022</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
